--- a/public/downloads/TPRM_Vendor_Scoring_PayWave.xlsx
+++ b/public/downloads/TPRM_Vendor_Scoring_PayWave.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Framework:</t>
   </si>
   <si>
-    <t xml:space="preserve">MAS TRM Guidelines Section 9, MAS Outsourcing Guidelines, ISO 27001:2022 A.5.19–A.5.22</t>
+    <t xml:space="preserve">MAS TRM Guidelines Section 9, MAS Guidelines on Outsourcing (Financial Institutions other than Banks), ISO 27001:2022 A.5.19–A.5.22</t>
   </si>
   <si>
     <t xml:space="preserve">Assessment Date:</t>
